--- a/input/Data_User_set.xlsx
+++ b/input/Data_User_set.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epish\PycharmProjects\endemo_git\pythonProject\draft_endemo\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epish\PycharmProjects\endemo_git\pythonProject\endemo\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2E366C-BC7E-4DA8-B563-493EA74015BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611F4BA8-5E8F-4BCF-AF68-C9D7441F415E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$AF$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$AF$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="90">
   <si>
     <t>Region</t>
   </si>
@@ -651,6 +651,123 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Data"/>
+      <sheetName val="Function options"/>
+      <sheetName val="info"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>lin</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>y = k0 + k1*DDr1 + k2*DDr2 + …</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>exp</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>interp_lin</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>lin interpolation between given points - based on driver as x-aches</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>const</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>y = const = k0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>const_last</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>y = const = y(t_hist)</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>const_mean</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>y = const = avg of all y(t_hist))</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>const_mult_div</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>y = k0 * (DDr1 / DDr2)</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>lin_mult_div</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>y = k0 + (k1 + k2*DDr1)*DDr2/DDr3</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>lin_share</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>y = k0 + (k1 + k2*DDr1)*DDr2</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>exp_mult_div</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3)) * DDr2/DDr3</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>mult</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>y = k0 + k1 *DDr1*DDr2*DDr3…</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>mult_k0_zero</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>y = k1 *DDr1*DDr2*DDr3…</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Data"/>
       <sheetName val="Sheet1"/>
       <sheetName val="Function options"/>
     </sheetNames>
@@ -787,123 +904,6 @@
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Data"/>
-      <sheetName val="Function options"/>
-      <sheetName val="info"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>lin</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>y = k0 + k1*DDr1 + k2*DDr2 + …</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>exp</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>interp_lin</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>lin interpolation between given points - based on driver as x-aches</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>const</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>y = const = k0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>const_last</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>y = const = y(t_hist)</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>const_mean</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>y = const = avg of all y(t_hist))</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>const_mult_div</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>y = k0 * (DDr1 / DDr2)</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>lin_mult_div</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>y = k0 + (k1 + k2*DDr1)*DDr2/DDr3</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>lin_share</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>y = k0 + (k1 + k2*DDr1)*DDr2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>exp_mult_div</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3)) * DDr2/DDr3</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>mult</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>y = k0 + k1 *DDr1*DDr2*DDr3…</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>mult_k0_zero</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>y = k1 *DDr1*DDr2*DDr3…</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1196,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04F4DADF-B8DF-48E5-BA19-53C996BFB8F9}">
-  <dimension ref="A1:AF102"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
@@ -1322,7 +1322,7 @@
         <v>74</v>
       </c>
       <c r="M2" t="str" cm="1">
-        <f t="array" ref="M2">_xlfn.XLOOKUP(L2, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M2">_xlfn.XLOOKUP(L2, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = k0 + (k1 + k2*DDr1)*DDr2</v>
       </c>
       <c r="N2" s="2" t="s">
@@ -1383,7 +1383,7 @@
         <v>58</v>
       </c>
       <c r="M3" t="str" cm="1">
-        <f t="array" ref="M3">_xlfn.XLOOKUP(L3, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M3">_xlfn.XLOOKUP(L3, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -1445,7 +1445,7 @@
         <v>58</v>
       </c>
       <c r="M4" t="str" cm="1">
-        <f t="array" ref="M4">_xlfn.XLOOKUP(L4, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M4">_xlfn.XLOOKUP(L4, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
       </c>
       <c r="N4" s="2" t="s">
@@ -1506,7 +1506,7 @@
         <v>58</v>
       </c>
       <c r="M5" t="str" cm="1">
-        <f t="array" ref="M5">_xlfn.XLOOKUP(L5, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M5">_xlfn.XLOOKUP(L5, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
       </c>
       <c r="N5" s="2" t="s">
@@ -1571,7 +1571,7 @@
         <v>50</v>
       </c>
       <c r="M6" t="str" cm="1">
-        <f t="array" ref="M6">_xlfn.XLOOKUP(L6, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M6">_xlfn.XLOOKUP(L6, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N6" s="2"/>
@@ -1617,7 +1617,7 @@
         <v>50</v>
       </c>
       <c r="M7" t="str" cm="1">
-        <f t="array" ref="M7">_xlfn.XLOOKUP(L7, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M7">_xlfn.XLOOKUP(L7, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N7" s="2"/>
@@ -1664,7 +1664,7 @@
         <v>50</v>
       </c>
       <c r="M8" t="str" cm="1">
-        <f t="array" ref="M8">_xlfn.XLOOKUP(L8, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M8">_xlfn.XLOOKUP(L8, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N8" s="2"/>
@@ -1710,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="M9" t="str" cm="1">
-        <f t="array" ref="M9">_xlfn.XLOOKUP(L9, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M9">_xlfn.XLOOKUP(L9, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N9" s="2"/>
@@ -1757,7 +1757,7 @@
         <v>50</v>
       </c>
       <c r="M10" t="str" cm="1">
-        <f t="array" ref="M10">_xlfn.XLOOKUP(L10, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M10">_xlfn.XLOOKUP(L10, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N10" s="2"/>
@@ -1786,40 +1786,52 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G11" s="5"/>
       <c r="J11" s="9"/>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="M11" t="str" cm="1">
-        <f t="array" ref="M11">_xlfn.XLOOKUP(L11, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
-        <v>y = const = y(t_hist)</v>
-      </c>
-      <c r="N11" s="2"/>
+        <f t="array" ref="M11">_xlfn.XLOOKUP(L11, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
+        <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="Q11" t="s">
         <v>25</v>
       </c>
       <c r="R11">
-        <f t="shared" ref="R11:R14" si="1">1/1000/3600</f>
+        <f t="shared" ref="R11:R13" si="1">1/1000/3600</f>
         <v>2.7777777777777776E-7</v>
       </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
       <c r="T11">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>-1</v>
+      </c>
+      <c r="V11">
+        <v>2020</v>
       </c>
       <c r="AE11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="AF11" s="16">
+        <f>1/2*T11</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
@@ -1839,7 +1851,7 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" s="5"/>
       <c r="J12" s="9"/>
@@ -1850,7 +1862,7 @@
         <v>58</v>
       </c>
       <c r="M12" t="str" cm="1">
-        <f t="array" ref="M12">_xlfn.XLOOKUP(L12, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M12">_xlfn.XLOOKUP(L12, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
       </c>
       <c r="N12" s="2" t="s">
@@ -1868,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1881,7 +1893,7 @@
       </c>
       <c r="AF12" s="16">
         <f>1/2*T12</f>
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
@@ -1901,7 +1913,7 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13" s="5"/>
       <c r="J13" s="9"/>
@@ -1912,7 +1924,7 @@
         <v>58</v>
       </c>
       <c r="M13" t="str" cm="1">
-        <f t="array" ref="M13">_xlfn.XLOOKUP(L13, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M13">_xlfn.XLOOKUP(L13, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
       </c>
       <c r="N13" s="2" t="s">
@@ -1930,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1941,9 +1953,8 @@
       <c r="AE13" t="s">
         <v>86</v>
       </c>
-      <c r="AF13" s="16">
-        <f>1/2*T13</f>
-        <v>3</v>
+      <c r="AF13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
@@ -1966,42 +1977,27 @@
         <v>18</v>
       </c>
       <c r="G14" s="5"/>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
       <c r="J14" s="9"/>
       <c r="K14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L14" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M14" t="str" cm="1">
-        <f t="array" ref="M14">_xlfn.XLOOKUP(L14, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
-        <v>y = k0 + k1 * ((1 + k2 / 100) ^ (DDr1 - k3))</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>42</v>
-      </c>
+        <f t="array" ref="M14">_xlfn.XLOOKUP(L14, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
+        <v>y = const = y(t_hist)</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="Q14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R14">
-        <f t="shared" si="1"/>
-        <v>2.7777777777777776E-7</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>-1</v>
-      </c>
-      <c r="V14">
-        <v>2020</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>86</v>
+        <v>0.01</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -2028,7 +2024,7 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" t="s">
@@ -2038,7 +2034,7 @@
         <v>50</v>
       </c>
       <c r="M15" t="str" cm="1">
-        <f t="array" ref="M15">_xlfn.XLOOKUP(L15, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M15">_xlfn.XLOOKUP(L15, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N15" s="2"/>
@@ -2074,7 +2070,7 @@
       </c>
       <c r="G16" s="5"/>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" t="s">
@@ -2084,7 +2080,7 @@
         <v>50</v>
       </c>
       <c r="M16" t="str" cm="1">
-        <f t="array" ref="M16">_xlfn.XLOOKUP(L16, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M16">_xlfn.XLOOKUP(L16, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N16" s="2"/>
@@ -2120,7 +2116,7 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" t="s">
@@ -2130,7 +2126,7 @@
         <v>50</v>
       </c>
       <c r="M17" t="str" cm="1">
-        <f t="array" ref="M17">_xlfn.XLOOKUP(L17, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M17">_xlfn.XLOOKUP(L17, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N17" s="2"/>
@@ -2166,7 +2162,7 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" t="s">
@@ -2176,7 +2172,7 @@
         <v>50</v>
       </c>
       <c r="M18" t="str" cm="1">
-        <f t="array" ref="M18">_xlfn.XLOOKUP(L18, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
+        <f t="array" ref="M18">_xlfn.XLOOKUP(L18, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
         <v>y = const = y(t_hist)</v>
       </c>
       <c r="N18" s="2"/>
@@ -2202,30 +2198,26 @@
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G19" s="5"/>
-      <c r="H19" t="s">
-        <v>24</v>
-      </c>
       <c r="J19" s="9"/>
       <c r="K19" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L19" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M19" t="str" cm="1">
-        <f t="array" ref="M19">_xlfn.XLOOKUP(L19, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
-        <v>y = const = y(t_hist)</v>
-      </c>
-      <c r="N19" s="2"/>
+        <f t="array" ref="M19">_xlfn.XLOOKUP(L19, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
+        <v>lin interpolation between given points - based on driver as x-aches</v>
+      </c>
+      <c r="N19" t="s">
+        <v>42</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="Q19" t="s">
         <v>26</v>
@@ -2233,6 +2225,15 @@
       <c r="R19">
         <v>0.01</v>
       </c>
+      <c r="Z19">
+        <v>100</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>86</v>
+      </c>
       <c r="AF19">
         <v>0</v>
       </c>
@@ -2248,142 +2249,189 @@
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
-      </c>
-      <c r="F20" t="s">
-        <v>19</v>
       </c>
       <c r="G20" s="5"/>
       <c r="J20" s="9"/>
       <c r="K20" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M20" t="str" cm="1">
-        <f t="array" ref="M20">_xlfn.XLOOKUP(L20, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
-        <v>y = const = y(t_hist)</v>
-      </c>
-      <c r="N20" s="2"/>
+        <f t="array" ref="M20">_xlfn.XLOOKUP(L20, '[1]Function options'!$A$2:$A$17, '[1]Function options'!$B$2:B$17, "Not found")</f>
+        <v>lin interpolation between given points - based on driver as x-aches</v>
+      </c>
+      <c r="N20" t="s">
+        <v>42</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="Q20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R20">
-        <f t="shared" ref="R20" si="2">1/1000/3600</f>
-        <v>2.7777777777777776E-7</v>
+        <v>0.01</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>100</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>86</v>
       </c>
       <c r="AF20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="J21" s="9"/>
-      <c r="K21" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21" t="s">
-        <v>47</v>
+      <c r="A21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="M21" t="str" cm="1">
-        <f t="array" ref="M21">_xlfn.XLOOKUP(L21, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
-        <v>lin interpolation between given points - based on driver as x-aches</v>
-      </c>
-      <c r="N21" t="s">
-        <v>42</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="Q21" t="s">
-        <v>26</v>
-      </c>
-      <c r="R21">
-        <v>0.01</v>
-      </c>
-      <c r="Z21">
-        <v>100</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
+        <f t="array" ref="M21">_xlfn.XLOOKUP(L21, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
+        <v>y = const = k0</v>
+      </c>
+      <c r="N21" s="11"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R21" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="S21" s="5">
+        <v>90.75</v>
+      </c>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
       <c r="AE21" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF21">
+        <v>85</v>
+      </c>
+      <c r="AF21" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="J22" s="9"/>
-      <c r="K22" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" t="s">
-        <v>47</v>
+      <c r="A22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="M22" t="str" cm="1">
-        <f t="array" ref="M22">_xlfn.XLOOKUP(L22, '[2]Function options'!$A$2:$A$17, '[2]Function options'!$B$2:B$17, "Not found")</f>
-        <v>lin interpolation between given points - based on driver as x-aches</v>
-      </c>
-      <c r="N22" t="s">
-        <v>42</v>
-      </c>
-      <c r="O22" s="2"/>
-      <c r="Q22" t="s">
-        <v>26</v>
-      </c>
-      <c r="R22">
-        <v>0.01</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>100</v>
-      </c>
+        <f t="array" ref="M22">_xlfn.XLOOKUP(L22, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
+        <v>y = const = k0</v>
+      </c>
+      <c r="N22" s="11"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="S22" s="5">
+        <v>90.75</v>
+      </c>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
       <c r="AE22" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="AF22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>8</v>
       </c>
@@ -2406,7 +2454,7 @@
         <v>77</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>8</v>
@@ -2421,12 +2469,10 @@
         <v>45</v>
       </c>
       <c r="M23" t="str" cm="1">
-        <f t="array" ref="M23">_xlfn.XLOOKUP(L23, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M23">_xlfn.XLOOKUP(L23, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N23" s="11"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
       <c r="Q23" s="5" t="s">
         <v>26</v>
       </c>
@@ -2436,17 +2482,6 @@
       <c r="S23" s="5">
         <v>90.75</v>
       </c>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="5"/>
-      <c r="AD23" s="5"/>
       <c r="AE23" t="s">
         <v>85</v>
       </c>
@@ -2454,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>8</v>
       </c>
@@ -2477,7 +2512,7 @@
         <v>77</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>8</v>
@@ -2492,12 +2527,10 @@
         <v>45</v>
       </c>
       <c r="M24" t="str" cm="1">
-        <f t="array" ref="M24">_xlfn.XLOOKUP(L24, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M24">_xlfn.XLOOKUP(L24, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N24" s="11"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
       <c r="Q24" s="5" t="s">
         <v>26</v>
       </c>
@@ -2507,17 +2540,6 @@
       <c r="S24" s="5">
         <v>90.75</v>
       </c>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="5"/>
       <c r="AE24" t="s">
         <v>85</v>
       </c>
@@ -2548,7 +2570,7 @@
         <v>77</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>8</v>
@@ -2563,7 +2585,7 @@
         <v>45</v>
       </c>
       <c r="M25" t="str" cm="1">
-        <f t="array" ref="M25">_xlfn.XLOOKUP(L25, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M25">_xlfn.XLOOKUP(L25, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N25" s="11"/>
@@ -2606,7 +2628,7 @@
         <v>77</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>8</v>
@@ -2621,7 +2643,7 @@
         <v>45</v>
       </c>
       <c r="M26" t="str" cm="1">
-        <f t="array" ref="M26">_xlfn.XLOOKUP(L26, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M26">_xlfn.XLOOKUP(L26, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N26" s="11"/>
@@ -2661,10 +2683,10 @@
         <v>18</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>8</v>
@@ -2679,7 +2701,7 @@
         <v>45</v>
       </c>
       <c r="M27" t="str" cm="1">
-        <f t="array" ref="M27">_xlfn.XLOOKUP(L27, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M27">_xlfn.XLOOKUP(L27, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N27" s="11"/>
@@ -2690,7 +2712,7 @@
         <v>0.01</v>
       </c>
       <c r="S27" s="5">
-        <v>90.75</v>
+        <v>90</v>
       </c>
       <c r="AE27" t="s">
         <v>85</v>
@@ -2719,10 +2741,10 @@
         <v>18</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>8</v>
@@ -2737,7 +2759,7 @@
         <v>45</v>
       </c>
       <c r="M28" t="str" cm="1">
-        <f t="array" ref="M28">_xlfn.XLOOKUP(L28, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M28">_xlfn.XLOOKUP(L28, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N28" s="11"/>
@@ -2748,7 +2770,7 @@
         <v>0.01</v>
       </c>
       <c r="S28" s="5">
-        <v>90.75</v>
+        <v>90</v>
       </c>
       <c r="AE28" t="s">
         <v>85</v>
@@ -2780,7 +2802,7 @@
         <v>78</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>8</v>
@@ -2795,7 +2817,7 @@
         <v>45</v>
       </c>
       <c r="M29" t="str" cm="1">
-        <f t="array" ref="M29">_xlfn.XLOOKUP(L29, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M29">_xlfn.XLOOKUP(L29, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N29" s="11"/>
@@ -2838,7 +2860,7 @@
         <v>78</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>8</v>
@@ -2853,7 +2875,7 @@
         <v>45</v>
       </c>
       <c r="M30" t="str" cm="1">
-        <f t="array" ref="M30">_xlfn.XLOOKUP(L30, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M30">_xlfn.XLOOKUP(L30, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N30" s="11"/>
@@ -2896,7 +2918,7 @@
         <v>78</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>8</v>
@@ -2911,7 +2933,7 @@
         <v>45</v>
       </c>
       <c r="M31" t="str" cm="1">
-        <f t="array" ref="M31">_xlfn.XLOOKUP(L31, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M31">_xlfn.XLOOKUP(L31, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N31" s="11"/>
@@ -2954,7 +2976,7 @@
         <v>78</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>8</v>
@@ -2969,7 +2991,7 @@
         <v>45</v>
       </c>
       <c r="M32" t="str" cm="1">
-        <f t="array" ref="M32">_xlfn.XLOOKUP(L32, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M32">_xlfn.XLOOKUP(L32, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N32" s="11"/>
@@ -3009,10 +3031,10 @@
         <v>18</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>8</v>
@@ -3027,7 +3049,7 @@
         <v>45</v>
       </c>
       <c r="M33" t="str" cm="1">
-        <f t="array" ref="M33">_xlfn.XLOOKUP(L33, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M33">_xlfn.XLOOKUP(L33, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N33" s="11"/>
@@ -3038,10 +3060,10 @@
         <v>0.01</v>
       </c>
       <c r="S33" s="5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AE33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF33" s="5">
         <v>0</v>
@@ -3067,10 +3089,10 @@
         <v>18</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>8</v>
@@ -3085,7 +3107,7 @@
         <v>45</v>
       </c>
       <c r="M34" t="str" cm="1">
-        <f t="array" ref="M34">_xlfn.XLOOKUP(L34, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M34">_xlfn.XLOOKUP(L34, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N34" s="11"/>
@@ -3096,10 +3118,10 @@
         <v>0.01</v>
       </c>
       <c r="S34" s="5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AE34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF34" s="5">
         <v>0</v>
@@ -3128,7 +3150,7 @@
         <v>79</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>8</v>
@@ -3143,7 +3165,7 @@
         <v>45</v>
       </c>
       <c r="M35" t="str" cm="1">
-        <f t="array" ref="M35">_xlfn.XLOOKUP(L35, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M35">_xlfn.XLOOKUP(L35, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N35" s="11"/>
@@ -3186,7 +3208,7 @@
         <v>79</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>8</v>
@@ -3201,7 +3223,7 @@
         <v>45</v>
       </c>
       <c r="M36" t="str" cm="1">
-        <f t="array" ref="M36">_xlfn.XLOOKUP(L36, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M36">_xlfn.XLOOKUP(L36, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N36" s="11"/>
@@ -3244,7 +3266,7 @@
         <v>79</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>8</v>
@@ -3259,7 +3281,7 @@
         <v>45</v>
       </c>
       <c r="M37" t="str" cm="1">
-        <f t="array" ref="M37">_xlfn.XLOOKUP(L37, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M37">_xlfn.XLOOKUP(L37, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N37" s="11"/>
@@ -3302,7 +3324,7 @@
         <v>79</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>8</v>
@@ -3317,7 +3339,7 @@
         <v>45</v>
       </c>
       <c r="M38" t="str" cm="1">
-        <f t="array" ref="M38">_xlfn.XLOOKUP(L38, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M38">_xlfn.XLOOKUP(L38, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N38" s="11"/>
@@ -3357,10 +3379,10 @@
         <v>18</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>8</v>
@@ -3375,7 +3397,7 @@
         <v>45</v>
       </c>
       <c r="M39" t="str" cm="1">
-        <f t="array" ref="M39">_xlfn.XLOOKUP(L39, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M39">_xlfn.XLOOKUP(L39, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N39" s="11"/>
@@ -3415,10 +3437,10 @@
         <v>18</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>8</v>
@@ -3433,7 +3455,7 @@
         <v>45</v>
       </c>
       <c r="M40" t="str" cm="1">
-        <f t="array" ref="M40">_xlfn.XLOOKUP(L40, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M40">_xlfn.XLOOKUP(L40, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N40" s="11"/>
@@ -3444,7 +3466,7 @@
         <v>0.01</v>
       </c>
       <c r="S40" s="5">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AE40" t="s">
         <v>86</v>
@@ -3476,7 +3498,7 @@
         <v>16</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>8</v>
@@ -3491,7 +3513,7 @@
         <v>45</v>
       </c>
       <c r="M41" t="str" cm="1">
-        <f t="array" ref="M41">_xlfn.XLOOKUP(L41, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M41">_xlfn.XLOOKUP(L41, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N41" s="11"/>
@@ -3502,7 +3524,7 @@
         <v>0.01</v>
       </c>
       <c r="S41" s="5">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AE41" t="s">
         <v>86</v>
@@ -3534,7 +3556,7 @@
         <v>16</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>8</v>
@@ -3549,7 +3571,7 @@
         <v>45</v>
       </c>
       <c r="M42" t="str" cm="1">
-        <f t="array" ref="M42">_xlfn.XLOOKUP(L42, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M42">_xlfn.XLOOKUP(L42, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N42" s="11"/>
@@ -3560,7 +3582,7 @@
         <v>0.01</v>
       </c>
       <c r="S42" s="5">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AE42" t="s">
         <v>86</v>
@@ -3592,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>8</v>
@@ -3607,7 +3629,7 @@
         <v>45</v>
       </c>
       <c r="M43" t="str" cm="1">
-        <f t="array" ref="M43">_xlfn.XLOOKUP(L43, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M43">_xlfn.XLOOKUP(L43, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N43" s="11"/>
@@ -3618,7 +3640,7 @@
         <v>0.01</v>
       </c>
       <c r="S43" s="5">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AE43" t="s">
         <v>86</v>
@@ -3650,7 +3672,7 @@
         <v>16</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>8</v>
@@ -3665,7 +3687,7 @@
         <v>45</v>
       </c>
       <c r="M44" t="str" cm="1">
-        <f t="array" ref="M44">_xlfn.XLOOKUP(L44, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M44">_xlfn.XLOOKUP(L44, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N44" s="11"/>
@@ -3702,13 +3724,13 @@
         <v>8</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>8</v>
@@ -3723,7 +3745,7 @@
         <v>45</v>
       </c>
       <c r="M45" t="str" cm="1">
-        <f t="array" ref="M45">_xlfn.XLOOKUP(L45, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M45">_xlfn.XLOOKUP(L45, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N45" s="11"/>
@@ -3763,10 +3785,10 @@
         <v>18</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>8</v>
@@ -3781,7 +3803,7 @@
         <v>45</v>
       </c>
       <c r="M46" t="str" cm="1">
-        <f t="array" ref="M46">_xlfn.XLOOKUP(L46, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M46">_xlfn.XLOOKUP(L46, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N46" s="11"/>
@@ -3792,10 +3814,10 @@
         <v>0.01</v>
       </c>
       <c r="S46" s="5">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="AE46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AF46" s="5">
         <v>0</v>
@@ -3818,13 +3840,13 @@
         <v>8</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>8</v>
@@ -3839,7 +3861,7 @@
         <v>45</v>
       </c>
       <c r="M47" t="str" cm="1">
-        <f t="array" ref="M47">_xlfn.XLOOKUP(L47, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M47">_xlfn.XLOOKUP(L47, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N47" s="11"/>
@@ -3850,10 +3872,10 @@
         <v>0.01</v>
       </c>
       <c r="S47" s="5">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="AE47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AF47" s="5">
         <v>0</v>
@@ -3882,7 +3904,7 @@
         <v>80</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>8</v>
@@ -3897,7 +3919,7 @@
         <v>45</v>
       </c>
       <c r="M48" t="str" cm="1">
-        <f t="array" ref="M48">_xlfn.XLOOKUP(L48, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M48">_xlfn.XLOOKUP(L48, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N48" s="11"/>
@@ -3940,7 +3962,7 @@
         <v>80</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>8</v>
@@ -3955,7 +3977,7 @@
         <v>45</v>
       </c>
       <c r="M49" t="str" cm="1">
-        <f t="array" ref="M49">_xlfn.XLOOKUP(L49, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M49">_xlfn.XLOOKUP(L49, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N49" s="11"/>
@@ -3998,7 +4020,7 @@
         <v>80</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>8</v>
@@ -4013,7 +4035,7 @@
         <v>45</v>
       </c>
       <c r="M50" t="str" cm="1">
-        <f t="array" ref="M50">_xlfn.XLOOKUP(L50, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M50">_xlfn.XLOOKUP(L50, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N50" s="11"/>
@@ -4056,7 +4078,7 @@
         <v>80</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>8</v>
@@ -4071,7 +4093,7 @@
         <v>45</v>
       </c>
       <c r="M51" t="str" cm="1">
-        <f t="array" ref="M51">_xlfn.XLOOKUP(L51, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M51">_xlfn.XLOOKUP(L51, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N51" s="11"/>
@@ -4110,11 +4132,11 @@
       <c r="F52" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>80</v>
+      <c r="G52" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>8</v>
@@ -4129,7 +4151,7 @@
         <v>45</v>
       </c>
       <c r="M52" t="str" cm="1">
-        <f t="array" ref="M52">_xlfn.XLOOKUP(L52, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M52">_xlfn.XLOOKUP(L52, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N52" s="11"/>
@@ -4140,10 +4162,10 @@
         <v>0.01</v>
       </c>
       <c r="S52" s="5">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AE52" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF52" s="5">
         <v>0</v>
@@ -4168,11 +4190,11 @@
       <c r="F53" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>80</v>
+      <c r="G53" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>8</v>
@@ -4187,7 +4209,7 @@
         <v>45</v>
       </c>
       <c r="M53" t="str" cm="1">
-        <f t="array" ref="M53">_xlfn.XLOOKUP(L53, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M53">_xlfn.XLOOKUP(L53, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N53" s="11"/>
@@ -4198,10 +4220,10 @@
         <v>0.01</v>
       </c>
       <c r="S53" s="5">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AE53" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF53" s="5">
         <v>0</v>
@@ -4230,7 +4252,7 @@
         <v>17</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>8</v>
@@ -4245,7 +4267,7 @@
         <v>45</v>
       </c>
       <c r="M54" t="str" cm="1">
-        <f t="array" ref="M54">_xlfn.XLOOKUP(L54, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M54">_xlfn.XLOOKUP(L54, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N54" s="11"/>
@@ -4288,7 +4310,7 @@
         <v>17</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>8</v>
@@ -4303,7 +4325,7 @@
         <v>45</v>
       </c>
       <c r="M55" t="str" cm="1">
-        <f t="array" ref="M55">_xlfn.XLOOKUP(L55, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M55">_xlfn.XLOOKUP(L55, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N55" s="11"/>
@@ -4346,7 +4368,7 @@
         <v>17</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>8</v>
@@ -4361,7 +4383,7 @@
         <v>45</v>
       </c>
       <c r="M56" t="str" cm="1">
-        <f t="array" ref="M56">_xlfn.XLOOKUP(L56, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M56">_xlfn.XLOOKUP(L56, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N56" s="11"/>
@@ -4404,7 +4426,7 @@
         <v>17</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>8</v>
@@ -4419,7 +4441,7 @@
         <v>45</v>
       </c>
       <c r="M57" t="str" cm="1">
-        <f t="array" ref="M57">_xlfn.XLOOKUP(L57, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M57">_xlfn.XLOOKUP(L57, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N57" s="11"/>
@@ -4455,14 +4477,14 @@
       <c r="E58" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" s="6" t="s">
+      <c r="F58" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="G58" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H58" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>8</v>
@@ -4476,8 +4498,8 @@
       <c r="L58" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M58" t="str" cm="1">
-        <f t="array" ref="M58">_xlfn.XLOOKUP(L58, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+      <c r="M58" s="5" t="str" cm="1">
+        <f t="array" ref="M58">_xlfn.XLOOKUP(L58, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N58" s="11"/>
@@ -4513,14 +4535,14 @@
       <c r="E59" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>18</v>
+      <c r="F59" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>8</v>
@@ -4534,8 +4556,8 @@
       <c r="L59" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M59" t="str" cm="1">
-        <f t="array" ref="M59">_xlfn.XLOOKUP(L59, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+      <c r="M59" s="5" t="str" cm="1">
+        <f t="array" ref="M59">_xlfn.XLOOKUP(L59, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>y = const = k0</v>
       </c>
       <c r="N59" s="11"/>
@@ -4560,13 +4582,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>8</v>
@@ -4586,25 +4608,39 @@
       <c r="J60" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="5" t="s">
-        <v>45</v>
+      <c r="K60" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="M60" s="5" t="str" cm="1">
-        <f t="array" ref="M60">_xlfn.XLOOKUP(L60, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
-        <v>y = const = k0</v>
-      </c>
-      <c r="N60" s="11"/>
+        <f t="array" ref="M60">_xlfn.XLOOKUP(L60, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
+        <v>lin interpolation between given points - based on driver as x-aches</v>
+      </c>
+      <c r="N60" s="11" t="s">
+        <v>42</v>
+      </c>
       <c r="Q60" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R60" s="5">
         <v>0.01</v>
       </c>
-      <c r="S60" s="5">
-        <v>100</v>
+      <c r="Z60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="5">
+        <v>0</v>
       </c>
       <c r="AE60" t="s">
         <v>86</v>
@@ -4618,25 +4654,25 @@
         <v>8</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>17</v>
+      <c r="F61" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>8</v>
@@ -4644,25 +4680,30 @@
       <c r="J61" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>45</v>
+      <c r="K61" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="M61" s="5" t="str" cm="1">
-        <f t="array" ref="M61">_xlfn.XLOOKUP(L61, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
-        <v>y = const = k0</v>
-      </c>
-      <c r="N61" s="11"/>
+        <f t="array" ref="M61">_xlfn.XLOOKUP(L61, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
+        <v>lin interpolation between given points - based on driver as x-aches</v>
+      </c>
+      <c r="N61" s="11" t="s">
+        <v>42</v>
+      </c>
       <c r="Q61" s="5" t="s">
         <v>26</v>
       </c>
       <c r="R61" s="5">
         <v>0.01</v>
       </c>
-      <c r="S61" s="5">
-        <v>100</v>
+      <c r="Z61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="5">
+        <v>50</v>
       </c>
       <c r="AE61" t="s">
         <v>86</v>
@@ -4687,14 +4728,14 @@
       <c r="E62" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>17</v>
+      <c r="F62" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>8</v>
@@ -4708,8 +4749,8 @@
       <c r="L62" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="M62" s="5" t="str" cm="1">
-        <f t="array" ref="M62">_xlfn.XLOOKUP(L62, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+      <c r="M62" t="str" cm="1">
+        <f t="array" ref="M62">_xlfn.XLOOKUP(L62, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N62" s="11" t="s">
@@ -4724,17 +4765,8 @@
       <c r="Z62" s="5">
         <v>0</v>
       </c>
-      <c r="AA62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="5">
-        <v>0</v>
-      </c>
       <c r="AC62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE62" t="s">
         <v>86</v>
@@ -4766,7 +4798,7 @@
         <v>16</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>8</v>
@@ -4780,8 +4812,8 @@
       <c r="L63" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="M63" s="5" t="str" cm="1">
-        <f t="array" ref="M63">_xlfn.XLOOKUP(L63, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+      <c r="M63" t="str" cm="1">
+        <f t="array" ref="M63">_xlfn.XLOOKUP(L63, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N63" s="11" t="s">
@@ -4797,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="AC63" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AE63" t="s">
         <v>86</v>
@@ -4829,7 +4861,7 @@
         <v>16</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>8</v>
@@ -4844,7 +4876,7 @@
         <v>47</v>
       </c>
       <c r="M64" t="str" cm="1">
-        <f t="array" ref="M64">_xlfn.XLOOKUP(L64, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M64">_xlfn.XLOOKUP(L64, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N64" s="11" t="s">
@@ -4860,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="AC64" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AE64" t="s">
         <v>86</v>
@@ -4892,7 +4924,7 @@
         <v>16</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>8</v>
@@ -4907,7 +4939,7 @@
         <v>47</v>
       </c>
       <c r="M65" t="str" cm="1">
-        <f t="array" ref="M65">_xlfn.XLOOKUP(L65, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M65">_xlfn.XLOOKUP(L65, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N65" s="11" t="s">
@@ -4937,7 +4969,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>8</v>
@@ -4949,13 +4981,13 @@
         <v>8</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>8</v>
@@ -4970,7 +5002,7 @@
         <v>47</v>
       </c>
       <c r="M66" t="str" cm="1">
-        <f t="array" ref="M66">_xlfn.XLOOKUP(L66, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M66">_xlfn.XLOOKUP(L66, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N66" s="11" t="s">
@@ -4983,10 +5015,19 @@
         <v>0.01</v>
       </c>
       <c r="Z66" s="5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="AA66" s="5">
+        <v>100</v>
+      </c>
+      <c r="AB66" s="5">
+        <v>100</v>
       </c>
       <c r="AC66" s="5">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="AD66" s="5">
+        <v>100</v>
       </c>
       <c r="AE66" t="s">
         <v>86</v>
@@ -5015,10 +5056,10 @@
         <v>18</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>8</v>
@@ -5033,7 +5074,7 @@
         <v>47</v>
       </c>
       <c r="M67" t="str" cm="1">
-        <f t="array" ref="M67">_xlfn.XLOOKUP(L67, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M67">_xlfn.XLOOKUP(L67, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N67" s="11" t="s">
@@ -5048,8 +5089,17 @@
       <c r="Z67" s="5">
         <v>0</v>
       </c>
+      <c r="AA67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="5">
+        <v>0</v>
+      </c>
       <c r="AC67" s="5">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="AD67" s="5">
+        <v>0</v>
       </c>
       <c r="AE67" t="s">
         <v>86</v>
@@ -5063,7 +5113,7 @@
         <v>8</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>8</v>
@@ -5075,13 +5125,13 @@
         <v>8</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I68" s="5" t="s">
         <v>8</v>
@@ -5096,7 +5146,7 @@
         <v>47</v>
       </c>
       <c r="M68" t="str" cm="1">
-        <f t="array" ref="M68">_xlfn.XLOOKUP(L68, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M68">_xlfn.XLOOKUP(L68, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N68" s="11" t="s">
@@ -5109,19 +5159,19 @@
         <v>0.01</v>
       </c>
       <c r="Z68" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA68" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB68" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC68" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD68" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="s">
         <v>86</v>
@@ -5153,7 +5203,7 @@
         <v>77</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>8</v>
@@ -5168,7 +5218,7 @@
         <v>47</v>
       </c>
       <c r="M69" t="str" cm="1">
-        <f t="array" ref="M69">_xlfn.XLOOKUP(L69, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M69">_xlfn.XLOOKUP(L69, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N69" s="11" t="s">
@@ -5225,7 +5275,7 @@
         <v>77</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>8</v>
@@ -5240,7 +5290,7 @@
         <v>47</v>
       </c>
       <c r="M70" t="str" cm="1">
-        <f t="array" ref="M70">_xlfn.XLOOKUP(L70, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M70">_xlfn.XLOOKUP(L70, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N70" s="11" t="s">
@@ -5297,7 +5347,7 @@
         <v>77</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>8</v>
@@ -5312,7 +5362,7 @@
         <v>47</v>
       </c>
       <c r="M71" t="str" cm="1">
-        <f t="array" ref="M71">_xlfn.XLOOKUP(L71, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M71">_xlfn.XLOOKUP(L71, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N71" s="11" t="s">
@@ -5369,7 +5419,7 @@
         <v>77</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>8</v>
@@ -5384,7 +5434,7 @@
         <v>47</v>
       </c>
       <c r="M72" t="str" cm="1">
-        <f t="array" ref="M72">_xlfn.XLOOKUP(L72, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M72">_xlfn.XLOOKUP(L72, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N72" s="11" t="s">
@@ -5438,10 +5488,10 @@
         <v>18</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I73" s="5" t="s">
         <v>8</v>
@@ -5456,7 +5506,7 @@
         <v>47</v>
       </c>
       <c r="M73" t="str" cm="1">
-        <f t="array" ref="M73">_xlfn.XLOOKUP(L73, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M73">_xlfn.XLOOKUP(L73, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N73" s="11" t="s">
@@ -5510,10 +5560,10 @@
         <v>18</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>8</v>
@@ -5528,7 +5578,7 @@
         <v>47</v>
       </c>
       <c r="M74" t="str" cm="1">
-        <f t="array" ref="M74">_xlfn.XLOOKUP(L74, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M74">_xlfn.XLOOKUP(L74, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N74" s="11" t="s">
@@ -5585,7 +5635,7 @@
         <v>78</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>8</v>
@@ -5600,7 +5650,7 @@
         <v>47</v>
       </c>
       <c r="M75" t="str" cm="1">
-        <f t="array" ref="M75">_xlfn.XLOOKUP(L75, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M75">_xlfn.XLOOKUP(L75, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N75" s="11" t="s">
@@ -5657,7 +5707,7 @@
         <v>78</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>8</v>
@@ -5672,7 +5722,7 @@
         <v>47</v>
       </c>
       <c r="M76" t="str" cm="1">
-        <f t="array" ref="M76">_xlfn.XLOOKUP(L76, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M76">_xlfn.XLOOKUP(L76, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N76" s="11" t="s">
@@ -5729,7 +5779,7 @@
         <v>78</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>8</v>
@@ -5744,7 +5794,7 @@
         <v>47</v>
       </c>
       <c r="M77" t="str" cm="1">
-        <f t="array" ref="M77">_xlfn.XLOOKUP(L77, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M77">_xlfn.XLOOKUP(L77, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N77" s="11" t="s">
@@ -5801,7 +5851,7 @@
         <v>78</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>8</v>
@@ -5816,7 +5866,7 @@
         <v>47</v>
       </c>
       <c r="M78" t="str" cm="1">
-        <f t="array" ref="M78">_xlfn.XLOOKUP(L78, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M78">_xlfn.XLOOKUP(L78, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N78" s="11" t="s">
@@ -5870,10 +5920,10 @@
         <v>18</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>8</v>
@@ -5888,7 +5938,7 @@
         <v>47</v>
       </c>
       <c r="M79" t="str" cm="1">
-        <f t="array" ref="M79">_xlfn.XLOOKUP(L79, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M79">_xlfn.XLOOKUP(L79, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N79" s="11" t="s">
@@ -5901,19 +5951,19 @@
         <v>0.01</v>
       </c>
       <c r="Z79" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA79" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB79" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC79" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD79" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE79" t="s">
         <v>86</v>
@@ -5942,10 +5992,10 @@
         <v>18</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>8</v>
@@ -5960,7 +6010,7 @@
         <v>47</v>
       </c>
       <c r="M80" t="str" cm="1">
-        <f t="array" ref="M80">_xlfn.XLOOKUP(L80, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M80">_xlfn.XLOOKUP(L80, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N80" s="11" t="s">
@@ -5973,18 +6023,9 @@
         <v>0.01</v>
       </c>
       <c r="Z80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC80" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="5">
         <v>0</v>
       </c>
       <c r="AE80" t="s">
@@ -6017,7 +6058,7 @@
         <v>80</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>8</v>
@@ -6032,7 +6073,7 @@
         <v>47</v>
       </c>
       <c r="M81" t="str" cm="1">
-        <f t="array" ref="M81">_xlfn.XLOOKUP(L81, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M81">_xlfn.XLOOKUP(L81, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N81" s="11" t="s">
@@ -6047,17 +6088,8 @@
       <c r="Z81" s="5">
         <v>100</v>
       </c>
-      <c r="AA81" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB81" s="5">
-        <v>100</v>
-      </c>
       <c r="AC81" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD81" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="s">
         <v>86</v>
@@ -6089,7 +6121,7 @@
         <v>80</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>8</v>
@@ -6104,7 +6136,7 @@
         <v>47</v>
       </c>
       <c r="M82" t="str" cm="1">
-        <f t="array" ref="M82">_xlfn.XLOOKUP(L82, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M82">_xlfn.XLOOKUP(L82, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N82" s="11" t="s">
@@ -6152,7 +6184,7 @@
         <v>80</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I83" s="5" t="s">
         <v>8</v>
@@ -6167,7 +6199,7 @@
         <v>47</v>
       </c>
       <c r="M83" t="str" cm="1">
-        <f t="array" ref="M83">_xlfn.XLOOKUP(L83, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M83">_xlfn.XLOOKUP(L83, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N83" s="11" t="s">
@@ -6215,7 +6247,7 @@
         <v>80</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>8</v>
@@ -6230,7 +6262,7 @@
         <v>47</v>
       </c>
       <c r="M84" t="str" cm="1">
-        <f t="array" ref="M84">_xlfn.XLOOKUP(L84, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M84">_xlfn.XLOOKUP(L84, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N84" s="11" t="s">
@@ -6274,11 +6306,11 @@
       <c r="F85" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G85" s="5" t="s">
-        <v>80</v>
+      <c r="G85" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I85" s="5" t="s">
         <v>8</v>
@@ -6293,7 +6325,7 @@
         <v>47</v>
       </c>
       <c r="M85" t="str" cm="1">
-        <f t="array" ref="M85">_xlfn.XLOOKUP(L85, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M85">_xlfn.XLOOKUP(L85, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N85" s="11" t="s">
@@ -6306,9 +6338,18 @@
         <v>0.01</v>
       </c>
       <c r="Z85" s="5">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="AA85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="5">
+        <v>0</v>
       </c>
       <c r="AC85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="5">
         <v>0</v>
       </c>
       <c r="AE85" t="s">
@@ -6337,11 +6378,11 @@
       <c r="F86" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>80</v>
+      <c r="G86" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I86" s="5" t="s">
         <v>8</v>
@@ -6356,7 +6397,7 @@
         <v>47</v>
       </c>
       <c r="M86" t="str" cm="1">
-        <f t="array" ref="M86">_xlfn.XLOOKUP(L86, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M86">_xlfn.XLOOKUP(L86, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N86" s="11" t="s">
@@ -6369,7 +6410,7 @@
         <v>0.01</v>
       </c>
       <c r="Z86" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC86" s="5">
         <v>0</v>
@@ -6404,7 +6445,7 @@
         <v>17</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>8</v>
@@ -6419,7 +6460,7 @@
         <v>47</v>
       </c>
       <c r="M87" t="str" cm="1">
-        <f t="array" ref="M87">_xlfn.XLOOKUP(L87, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M87">_xlfn.XLOOKUP(L87, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N87" s="11" t="s">
@@ -6434,16 +6475,7 @@
       <c r="Z87" s="5">
         <v>0</v>
       </c>
-      <c r="AA87" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB87" s="5">
-        <v>0</v>
-      </c>
       <c r="AC87" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD87" s="5">
         <v>0</v>
       </c>
       <c r="AE87" t="s">
@@ -6476,7 +6508,7 @@
         <v>17</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I88" s="5" t="s">
         <v>8</v>
@@ -6491,7 +6523,7 @@
         <v>47</v>
       </c>
       <c r="M88" t="str" cm="1">
-        <f t="array" ref="M88">_xlfn.XLOOKUP(L88, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M88">_xlfn.XLOOKUP(L88, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N88" s="11" t="s">
@@ -6507,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="AC88" s="5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AE88" t="s">
         <v>86</v>
@@ -6539,7 +6571,7 @@
         <v>17</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I89" s="5" t="s">
         <v>8</v>
@@ -6554,7 +6586,7 @@
         <v>47</v>
       </c>
       <c r="M89" t="str" cm="1">
-        <f t="array" ref="M89">_xlfn.XLOOKUP(L89, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M89">_xlfn.XLOOKUP(L89, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N89" s="11" t="s">
@@ -6570,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="AC89" s="5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AE89" t="s">
         <v>86</v>
@@ -6602,7 +6634,7 @@
         <v>17</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I90" s="5" t="s">
         <v>8</v>
@@ -6617,7 +6649,7 @@
         <v>47</v>
       </c>
       <c r="M90" t="str" cm="1">
-        <f t="array" ref="M90">_xlfn.XLOOKUP(L90, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M90">_xlfn.XLOOKUP(L90, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N90" s="11" t="s">
@@ -6661,11 +6693,11 @@
       <c r="F91" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>17</v>
+      <c r="G91" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I91" s="5" t="s">
         <v>8</v>
@@ -6680,7 +6712,7 @@
         <v>47</v>
       </c>
       <c r="M91" t="str" cm="1">
-        <f t="array" ref="M91">_xlfn.XLOOKUP(L91, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M91">_xlfn.XLOOKUP(L91, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N91" s="11" t="s">
@@ -6695,8 +6727,17 @@
       <c r="Z91" s="5">
         <v>0</v>
       </c>
+      <c r="AA91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="5">
+        <v>0</v>
+      </c>
       <c r="AC91" s="5">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="AD91" s="5">
+        <v>0</v>
       </c>
       <c r="AE91" t="s">
         <v>86</v>
@@ -6724,11 +6765,11 @@
       <c r="F92" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G92" s="6" t="s">
-        <v>17</v>
+      <c r="G92" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I92" s="5" t="s">
         <v>8</v>
@@ -6743,7 +6784,7 @@
         <v>47</v>
       </c>
       <c r="M92" t="str" cm="1">
-        <f t="array" ref="M92">_xlfn.XLOOKUP(L92, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M92">_xlfn.XLOOKUP(L92, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N92" s="11" t="s">
@@ -6759,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="AC92" s="5">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AE92" t="s">
         <v>86</v>
@@ -6768,7 +6809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:32" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>8</v>
       </c>
@@ -6791,7 +6832,7 @@
         <v>79</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I93" s="5" t="s">
         <v>8</v>
@@ -6806,7 +6847,7 @@
         <v>47</v>
       </c>
       <c r="M93" t="str" cm="1">
-        <f t="array" ref="M93">_xlfn.XLOOKUP(L93, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M93">_xlfn.XLOOKUP(L93, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N93" s="11" t="s">
@@ -6821,17 +6862,8 @@
       <c r="Z93" s="5">
         <v>0</v>
       </c>
-      <c r="AA93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="5">
-        <v>0</v>
-      </c>
       <c r="AC93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD93" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE93" t="s">
         <v>86</v>
@@ -6863,7 +6895,7 @@
         <v>79</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I94" s="5" t="s">
         <v>8</v>
@@ -6878,7 +6910,7 @@
         <v>47</v>
       </c>
       <c r="M94" t="str" cm="1">
-        <f t="array" ref="M94">_xlfn.XLOOKUP(L94, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M94">_xlfn.XLOOKUP(L94, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N94" s="11" t="s">
@@ -6894,7 +6926,7 @@
         <v>0</v>
       </c>
       <c r="AC94" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="s">
         <v>86</v>
@@ -6903,7 +6935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:32" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>8</v>
       </c>
@@ -6926,7 +6958,7 @@
         <v>79</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I95" s="5" t="s">
         <v>8</v>
@@ -6941,7 +6973,7 @@
         <v>47</v>
       </c>
       <c r="M95" t="str" cm="1">
-        <f t="array" ref="M95">_xlfn.XLOOKUP(L95, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M95">_xlfn.XLOOKUP(L95, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N95" s="11" t="s">
@@ -6957,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="AC95" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="s">
         <v>86</v>
@@ -6989,7 +7021,7 @@
         <v>79</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I96" s="5" t="s">
         <v>8</v>
@@ -7004,7 +7036,7 @@
         <v>47</v>
       </c>
       <c r="M96" t="str" cm="1">
-        <f t="array" ref="M96">_xlfn.XLOOKUP(L96, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M96">_xlfn.XLOOKUP(L96, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N96" s="11" t="s">
@@ -7034,7 +7066,7 @@
         <v>8</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>8</v>
@@ -7049,10 +7081,10 @@
         <v>18</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I97" s="5" t="s">
         <v>8</v>
@@ -7067,7 +7099,7 @@
         <v>47</v>
       </c>
       <c r="M97" t="str" cm="1">
-        <f t="array" ref="M97">_xlfn.XLOOKUP(L97, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M97">_xlfn.XLOOKUP(L97, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N97" s="11" t="s">
@@ -7080,10 +7112,19 @@
         <v>0.01</v>
       </c>
       <c r="Z97" s="5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="AA97" s="5">
+        <v>100</v>
+      </c>
+      <c r="AB97" s="5">
+        <v>100</v>
       </c>
       <c r="AC97" s="5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="AD97" s="5">
+        <v>100</v>
       </c>
       <c r="AE97" t="s">
         <v>86</v>
@@ -7097,7 +7138,7 @@
         <v>8</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>8</v>
@@ -7108,14 +7149,14 @@
       <c r="E98" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F98" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>79</v>
+      <c r="F98" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I98" s="5" t="s">
         <v>8</v>
@@ -7130,7 +7171,7 @@
         <v>47</v>
       </c>
       <c r="M98" t="str" cm="1">
-        <f t="array" ref="M98">_xlfn.XLOOKUP(L98, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
+        <f t="array" ref="M98">_xlfn.XLOOKUP(L98, '[2]Function options'!$A$2:$A$21, '[2]Function options'!$B$2:B$21, "Not found")</f>
         <v>lin interpolation between given points - based on driver as x-aches</v>
       </c>
       <c r="N98" s="11" t="s">
@@ -7143,10 +7184,19 @@
         <v>0.01</v>
       </c>
       <c r="Z98" s="5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="AA98" s="5">
+        <v>100</v>
+      </c>
+      <c r="AB98" s="5">
+        <v>100</v>
       </c>
       <c r="AC98" s="5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="AD98" s="5">
+        <v>100</v>
       </c>
       <c r="AE98" t="s">
         <v>86</v>
@@ -7156,202 +7206,58 @@
       </c>
     </row>
     <row r="99" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I99" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J99" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M99" t="str" cm="1">
-        <f t="array" ref="M99">_xlfn.XLOOKUP(L99, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
-        <v>lin interpolation between given points - based on driver as x-aches</v>
-      </c>
-      <c r="N99" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q99" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="R99" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="Z99" s="5">
-        <v>100</v>
-      </c>
-      <c r="AA99" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB99" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC99" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD99" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE99" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF99" s="5">
-        <v>0</v>
-      </c>
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
+      <c r="L99"/>
+      <c r="M99"/>
+      <c r="N99"/>
+      <c r="O99"/>
+      <c r="P99"/>
+      <c r="Q99"/>
+      <c r="R99"/>
+      <c r="S99"/>
+      <c r="T99"/>
+      <c r="U99"/>
+      <c r="V99"/>
+      <c r="W99"/>
+      <c r="X99"/>
+      <c r="Y99"/>
+      <c r="Z99"/>
+      <c r="AA99"/>
+      <c r="AB99"/>
+      <c r="AC99"/>
+      <c r="AD99"/>
+      <c r="AE99"/>
+      <c r="AF99"/>
     </row>
     <row r="100" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I100" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M100" t="str" cm="1">
-        <f t="array" ref="M100">_xlfn.XLOOKUP(L100, '[1]Function options'!$A$2:$A$21, '[1]Function options'!$B$2:B$21, "Not found")</f>
-        <v>lin interpolation between given points - based on driver as x-aches</v>
-      </c>
-      <c r="N100" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q100" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="R100" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="Z100" s="5">
-        <v>100</v>
-      </c>
-      <c r="AA100" s="5">
-        <v>100</v>
-      </c>
-      <c r="AB100" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC100" s="5">
-        <v>100</v>
-      </c>
-      <c r="AD100" s="5">
-        <v>100</v>
-      </c>
-      <c r="AE100" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF100" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A101"/>
-      <c r="B101"/>
-      <c r="C101"/>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
-      <c r="I101"/>
-      <c r="J101"/>
-      <c r="K101"/>
-      <c r="L101"/>
-      <c r="M101"/>
-      <c r="N101"/>
-      <c r="O101"/>
-      <c r="P101"/>
-      <c r="Q101"/>
-      <c r="R101"/>
-      <c r="S101"/>
-      <c r="T101"/>
-      <c r="U101"/>
-      <c r="V101"/>
-      <c r="W101"/>
-      <c r="X101"/>
-      <c r="Y101"/>
-      <c r="Z101"/>
-      <c r="AA101"/>
-      <c r="AB101"/>
-      <c r="AC101"/>
-      <c r="AD101"/>
-      <c r="AE101"/>
-      <c r="AF101"/>
-    </row>
-    <row r="102" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102"/>
-      <c r="N102" s="11"/>
-      <c r="AE102"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100"/>
+      <c r="N100" s="11"/>
+      <c r="AE100"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF102" xr:uid="{04F4DADF-B8DF-48E5-BA19-53C996BFB8F9}"/>
+  <autoFilter ref="A1:AF100" xr:uid="{04F4DADF-B8DF-48E5-BA19-53C996BFB8F9}"/>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mathematical explanation of the selected function on the left." sqref="M1" xr:uid="{CC9C77C0-C9ED-476A-B41B-E0FF51A9AB9F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select function from the drop-down menu. Mathematical explanation of the function is given in the Equation field on the right." sqref="L1" xr:uid="{69AE46A0-3B41-40C8-BF79-75E82F1413C0}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K22" xr:uid="{67A55523-1C34-46D3-A5F7-C63D0D171602}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N100:P100 N2:P98" xr:uid="{2D67A3F9-7866-48AD-8855-A05268888064}">
+      <formula1>"TIME, POP, GDP, SIZE_HH, ELEC_PR, m2_HH, HW_PER_CAP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K20" xr:uid="{67A55523-1C34-46D3-A5F7-C63D0D171602}">
       <formula1>"Historical, User"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N102:P102 N2:P100" xr:uid="{2D67A3F9-7866-48AD-8855-A05268888064}">
-      <formula1>"TIME, POP, GDP, SIZE_HH, ELEC_PR, m2_HH, HW_PER_CAP"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
